--- a/work_info.xlsx
+++ b/work_info.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bmekala\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bmekala\Desktop\DataFactZ_HRMS\datafactz\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,7 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AD$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AD$53</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="405">
   <si>
     <t>Badge ID</t>
   </si>
@@ -277,9 +277,6 @@
     <t xml:space="preserve">vignesh.suryadevara@datafactz.com </t>
   </si>
   <si>
-    <t xml:space="preserve">bhavana.chinnabalannagari@datafactz.com </t>
-  </si>
-  <si>
     <t xml:space="preserve">rakesh.madadi@datafactz.com </t>
   </si>
   <si>
@@ -703,9 +700,6 @@
     <t>Phoenix Info City </t>
   </si>
   <si>
-    <t>Yellareddyguda</t>
-  </si>
-  <si>
     <t>Kalkaji</t>
   </si>
   <si>
@@ -922,9 +916,6 @@
     <t>Sushma</t>
   </si>
   <si>
-    <t>Surendra Reddy Chinnabalannagari</t>
-  </si>
-  <si>
     <t>Madadi Sridhar Reddy</t>
   </si>
   <si>
@@ -958,9 +949,6 @@
     <t> 524002005</t>
   </si>
   <si>
-    <t>First Name</t>
-  </si>
-  <si>
     <t>Karthik</t>
   </si>
   <si>
@@ -1084,9 +1072,6 @@
     <t>Vignesh</t>
   </si>
   <si>
-    <t>Bhavana</t>
-  </si>
-  <si>
     <t>Rakesh</t>
   </si>
   <si>
@@ -1108,9 +1093,6 @@
     <t>Nitil</t>
   </si>
   <si>
-    <t>Last Name</t>
-  </si>
-  <si>
     <t>Kayala</t>
   </si>
   <si>
@@ -1243,9 +1225,6 @@
     <t>Suryadevara</t>
   </si>
   <si>
-    <t>Chinnabalannagari</t>
-  </si>
-  <si>
     <t>Madadi</t>
   </si>
   <si>
@@ -1265,6 +1244,12 @@
   </si>
   <si>
     <t>Singh</t>
+  </si>
+  <si>
+    <t>employee_last_name</t>
+  </si>
+  <si>
+    <t>employee_first_name</t>
   </si>
 </sst>
 </file>
@@ -1302,7 +1287,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -1310,11 +1294,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="7"/>
+      <color rgb="FF94C1FA"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1365,7 +1348,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1442,9 +1425,6 @@
     <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="12" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1457,8 +1437,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1765,7 +1745,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AF54"/>
+  <dimension ref="A1:AF53"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.26953125" style="7" bestFit="1" customWidth="1"/>
@@ -1892,10 +1872,10 @@
         <v>34</v>
       </c>
       <c r="AE1" s="30" t="s">
-        <v>307</v>
+        <v>404</v>
       </c>
       <c r="AF1" s="30" t="s">
-        <v>357</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -1924,7 +1904,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" s="10">
         <v>1</v>
@@ -1942,16 +1922,16 @@
         <v>100</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q2" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="R2" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="S2" s="8">
         <v>500229034</v>
@@ -1963,10 +1943,10 @@
         <v>24</v>
       </c>
       <c r="V2" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W2" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>36</v>
@@ -1981,19 +1961,19 @@
         <v>9701924657</v>
       </c>
       <c r="AB2" s="8" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AC2" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD2" s="12">
         <v>41436</v>
       </c>
-      <c r="AE2" s="31" t="s">
-        <v>308</v>
-      </c>
-      <c r="AF2" s="31" t="s">
-        <v>358</v>
+      <c r="AE2" s="29" t="s">
+        <v>304</v>
+      </c>
+      <c r="AF2" s="29" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -2022,7 +2002,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J3" s="10">
         <v>1</v>
@@ -2040,16 +2020,16 @@
         <v>100</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="S3" s="8">
         <v>500229034</v>
@@ -2061,10 +2041,10 @@
         <v>24</v>
       </c>
       <c r="V3" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W3" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="X3" s="8" t="s">
         <v>37</v>
@@ -2079,19 +2059,19 @@
         <v>7032707096</v>
       </c>
       <c r="AB3" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AC3" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD3" s="13">
         <v>41892</v>
       </c>
-      <c r="AE3" s="31" t="s">
-        <v>309</v>
-      </c>
-      <c r="AF3" s="31" t="s">
-        <v>359</v>
+      <c r="AE3" s="29" t="s">
+        <v>305</v>
+      </c>
+      <c r="AF3" s="29" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="4" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -2120,7 +2100,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" s="10">
         <v>1</v>
@@ -2138,19 +2118,19 @@
         <v>100</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="R4" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="S4" s="8" t="s">
         <v>91</v>
-      </c>
-      <c r="S4" s="8" t="s">
-        <v>92</v>
       </c>
       <c r="T4" s="9" t="s">
         <v>23</v>
@@ -2159,10 +2139,10 @@
         <v>24</v>
       </c>
       <c r="V4" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W4" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="X4" s="8" t="s">
         <v>38</v>
@@ -2177,19 +2157,19 @@
         <v>9701890909</v>
       </c>
       <c r="AB4" s="10" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AC4" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD4" s="12">
         <v>42114</v>
       </c>
-      <c r="AE4" s="31" t="s">
-        <v>279</v>
-      </c>
-      <c r="AF4" s="31" t="s">
-        <v>360</v>
+      <c r="AE4" s="29" t="s">
+        <v>277</v>
+      </c>
+      <c r="AF4" s="29" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="5" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -2218,7 +2198,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" s="10">
         <v>1</v>
@@ -2236,16 +2216,16 @@
         <v>100</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="S5" s="8">
         <v>502229059</v>
@@ -2257,16 +2237,16 @@
         <v>24</v>
       </c>
       <c r="V5" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W5" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="X5" s="3" t="s">
         <v>39</v>
       </c>
       <c r="Y5" s="10" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z5" s="9">
         <v>0</v>
@@ -2275,19 +2255,19 @@
         <v>9848727690</v>
       </c>
       <c r="AB5" s="10" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AC5" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD5" s="13">
         <v>43374</v>
       </c>
-      <c r="AE5" s="31" t="s">
-        <v>310</v>
-      </c>
-      <c r="AF5" s="31" t="s">
-        <v>361</v>
+      <c r="AE5" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="AF5" s="29" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="6" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -2316,7 +2296,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J6" s="10">
         <v>1</v>
@@ -2334,16 +2314,16 @@
         <v>100</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q6" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="S6" s="8">
         <v>500229099</v>
@@ -2355,16 +2335,16 @@
         <v>24</v>
       </c>
       <c r="V6" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W6" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="X6" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y6" s="10" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z6" s="9">
         <v>0</v>
@@ -2373,19 +2353,19 @@
         <v>9441758967</v>
       </c>
       <c r="AB6" s="10" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AC6" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD6" s="13">
         <v>43682</v>
       </c>
-      <c r="AE6" s="31" t="s">
-        <v>311</v>
-      </c>
-      <c r="AF6" s="31" t="s">
-        <v>362</v>
+      <c r="AE6" s="29" t="s">
+        <v>307</v>
+      </c>
+      <c r="AF6" s="29" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="7" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -2414,7 +2394,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J7" s="10">
         <v>1</v>
@@ -2432,16 +2412,16 @@
         <v>100</v>
       </c>
       <c r="O7" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R7" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="S7" s="8">
         <v>500229059</v>
@@ -2453,10 +2433,10 @@
         <v>24</v>
       </c>
       <c r="V7" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W7" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="X7" s="3" t="s">
         <v>41</v>
@@ -2471,19 +2451,19 @@
         <v>8317538084</v>
       </c>
       <c r="AB7" s="10" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AC7" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD7" s="13">
         <v>43794</v>
       </c>
-      <c r="AE7" s="31" t="s">
-        <v>312</v>
-      </c>
-      <c r="AF7" s="31" t="s">
-        <v>363</v>
+      <c r="AE7" s="29" t="s">
+        <v>308</v>
+      </c>
+      <c r="AF7" s="29" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="8" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -2512,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J8" s="10">
         <v>1</v>
@@ -2530,16 +2510,16 @@
         <v>100</v>
       </c>
       <c r="O8" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P8" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q8" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S8" s="2">
         <v>520229005</v>
@@ -2548,13 +2528,13 @@
         <v>23</v>
       </c>
       <c r="U8" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="V8" s="9" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="W8" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="X8" s="3" t="s">
         <v>42</v>
@@ -2569,19 +2549,19 @@
         <v>9885450131</v>
       </c>
       <c r="AB8" s="10" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AC8" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD8" s="13">
         <v>44383</v>
       </c>
-      <c r="AE8" s="31" t="s">
-        <v>313</v>
-      </c>
-      <c r="AF8" s="31" t="s">
-        <v>364</v>
+      <c r="AE8" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="AF8" s="29" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="9" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -2610,7 +2590,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" s="10">
         <v>1</v>
@@ -2628,16 +2608,16 @@
         <v>100</v>
       </c>
       <c r="O9" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="R9" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S9" s="4">
         <v>560229030</v>
@@ -2646,13 +2626,13 @@
         <v>23</v>
       </c>
       <c r="U9" s="9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V9" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="X9" s="4" t="s">
         <v>43</v>
@@ -2667,19 +2647,19 @@
         <v>9398819243</v>
       </c>
       <c r="AB9" s="10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AC9" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD9" s="13">
         <v>44418</v>
       </c>
-      <c r="AE9" s="31" t="s">
-        <v>314</v>
-      </c>
-      <c r="AF9" s="31" t="s">
-        <v>365</v>
+      <c r="AE9" s="29" t="s">
+        <v>310</v>
+      </c>
+      <c r="AF9" s="29" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="10" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -2708,7 +2688,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10" s="10">
         <v>1</v>
@@ -2726,16 +2706,16 @@
         <v>100</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="S10" s="8">
         <v>500229003</v>
@@ -2747,10 +2727,10 @@
         <v>24</v>
       </c>
       <c r="V10" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="X10" s="4" t="s">
         <v>44</v>
@@ -2765,19 +2745,19 @@
         <v>9346283767</v>
       </c>
       <c r="AB10" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AC10" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD10" s="13">
         <v>44420</v>
       </c>
-      <c r="AE10" s="31" t="s">
-        <v>315</v>
-      </c>
-      <c r="AF10" s="31" t="s">
-        <v>366</v>
+      <c r="AE10" s="29" t="s">
+        <v>311</v>
+      </c>
+      <c r="AF10" s="29" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="11" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -2806,7 +2786,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11" s="10">
         <v>1</v>
@@ -2824,16 +2804,16 @@
         <v>100</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="S11" s="8">
         <v>500240104</v>
@@ -2845,16 +2825,16 @@
         <v>24</v>
       </c>
       <c r="V11" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W11" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="X11" s="4" t="s">
         <v>45</v>
       </c>
       <c r="Y11" s="10" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z11" s="9">
         <v>0</v>
@@ -2863,19 +2843,19 @@
         <v>8688110551</v>
       </c>
       <c r="AB11" s="10" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AC11" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD11" s="13">
         <v>44426</v>
       </c>
-      <c r="AE11" s="31" t="s">
-        <v>316</v>
-      </c>
-      <c r="AF11" s="31" t="s">
-        <v>367</v>
+      <c r="AE11" s="29" t="s">
+        <v>312</v>
+      </c>
+      <c r="AF11" s="29" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="12" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -2904,7 +2884,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J12" s="10">
         <v>1</v>
@@ -2922,19 +2902,19 @@
         <v>100</v>
       </c>
       <c r="O12" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P12" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q12" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R12" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="S12" s="10" t="s">
         <v>99</v>
-      </c>
-      <c r="S12" s="10" t="s">
-        <v>100</v>
       </c>
       <c r="T12" s="9" t="s">
         <v>23</v>
@@ -2943,16 +2923,16 @@
         <v>24</v>
       </c>
       <c r="V12" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W12" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="X12" s="5" t="s">
         <v>46</v>
       </c>
       <c r="Y12" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z12" s="9">
         <v>0</v>
@@ -2961,19 +2941,19 @@
         <v>9014889688</v>
       </c>
       <c r="AB12" s="8" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AC12" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD12" s="12">
         <v>44480</v>
       </c>
-      <c r="AE12" s="31" t="s">
-        <v>317</v>
-      </c>
-      <c r="AF12" s="31" t="s">
-        <v>368</v>
+      <c r="AE12" s="29" t="s">
+        <v>313</v>
+      </c>
+      <c r="AF12" s="29" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="13" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -3002,7 +2982,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J13" s="10">
         <v>1</v>
@@ -3020,16 +3000,16 @@
         <v>100</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q13" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R13" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S13" s="8">
         <v>500229105</v>
@@ -3041,16 +3021,16 @@
         <v>24</v>
       </c>
       <c r="V13" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W13" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="X13" s="5" t="s">
         <v>47</v>
       </c>
       <c r="Y13" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z13" s="9">
         <v>0</v>
@@ -3059,19 +3039,19 @@
         <v>9347803336</v>
       </c>
       <c r="AB13" s="8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AC13" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD13" s="12">
         <v>44480</v>
       </c>
-      <c r="AE13" s="31" t="s">
-        <v>318</v>
-      </c>
-      <c r="AF13" s="31" t="s">
-        <v>369</v>
+      <c r="AE13" s="29" t="s">
+        <v>314</v>
+      </c>
+      <c r="AF13" s="29" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="14" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -3100,7 +3080,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" s="10">
         <v>1</v>
@@ -3118,16 +3098,16 @@
         <v>100</v>
       </c>
       <c r="O14" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P14" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="R14" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S14" s="10">
         <v>500229105</v>
@@ -3139,16 +3119,16 @@
         <v>24</v>
       </c>
       <c r="V14" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W14" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="X14" s="5" t="s">
         <v>48</v>
       </c>
       <c r="Y14" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z14" s="9">
         <v>0</v>
@@ -3157,19 +3137,19 @@
         <v>9885273431</v>
       </c>
       <c r="AB14" s="8" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AC14" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD14" s="12">
         <v>44480</v>
       </c>
-      <c r="AE14" s="31" t="s">
-        <v>319</v>
-      </c>
-      <c r="AF14" s="31" t="s">
-        <v>370</v>
+      <c r="AE14" s="29" t="s">
+        <v>315</v>
+      </c>
+      <c r="AF14" s="29" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="15" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -3198,7 +3178,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="10">
         <v>1</v>
@@ -3216,16 +3196,16 @@
         <v>100</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q15" s="16" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="R15" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S15" s="17">
         <v>500229105</v>
@@ -3237,16 +3217,16 @@
         <v>24</v>
       </c>
       <c r="V15" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="X15" s="5" t="s">
         <v>49</v>
       </c>
       <c r="Y15" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z15" s="9">
         <v>0</v>
@@ -3255,19 +3235,19 @@
         <v>9182175225</v>
       </c>
       <c r="AB15" s="8" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AC15" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD15" s="12">
         <v>44480</v>
       </c>
-      <c r="AE15" s="31" t="s">
-        <v>320</v>
-      </c>
-      <c r="AF15" s="31" t="s">
-        <v>371</v>
+      <c r="AE15" s="29" t="s">
+        <v>316</v>
+      </c>
+      <c r="AF15" s="29" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="16" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -3296,7 +3276,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J16" s="10">
         <v>1</v>
@@ -3314,19 +3294,19 @@
         <v>100</v>
       </c>
       <c r="O16" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P16" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q16" s="16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="R16" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="S16" s="17" t="s">
         <v>102</v>
-      </c>
-      <c r="S16" s="17" t="s">
-        <v>103</v>
       </c>
       <c r="T16" s="9" t="s">
         <v>23</v>
@@ -3335,16 +3315,16 @@
         <v>24</v>
       </c>
       <c r="V16" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W16" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="X16" s="5" t="s">
         <v>50</v>
       </c>
       <c r="Y16" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z16" s="9">
         <v>0</v>
@@ -3353,19 +3333,19 @@
         <v>8143010161</v>
       </c>
       <c r="AB16" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="AC16" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD16" s="12">
         <v>44487</v>
       </c>
-      <c r="AE16" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="AF16" s="31" t="s">
-        <v>372</v>
+      <c r="AE16" s="29" t="s">
+        <v>317</v>
+      </c>
+      <c r="AF16" s="29" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="17" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -3394,7 +3374,7 @@
         <v>1</v>
       </c>
       <c r="I17" s="9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J17" s="10">
         <v>1</v>
@@ -3412,19 +3392,19 @@
         <v>100</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="R17" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T17" s="9" t="s">
         <v>23</v>
@@ -3433,16 +3413,16 @@
         <v>24</v>
       </c>
       <c r="V17" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W17" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="X17" s="5" t="s">
         <v>51</v>
       </c>
       <c r="Y17" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z17" s="9">
         <v>0</v>
@@ -3451,19 +3431,19 @@
         <v>8500862104</v>
       </c>
       <c r="AB17" s="8" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="AC17" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD17" s="12">
         <v>44487</v>
       </c>
-      <c r="AE17" s="31" t="s">
-        <v>322</v>
-      </c>
-      <c r="AF17" s="31" t="s">
-        <v>373</v>
+      <c r="AE17" s="29" t="s">
+        <v>318</v>
+      </c>
+      <c r="AF17" s="29" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="18" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -3492,7 +3472,7 @@
         <v>1</v>
       </c>
       <c r="I18" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" s="10">
         <v>1</v>
@@ -3510,19 +3490,19 @@
         <v>100</v>
       </c>
       <c r="O18" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P18" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q18" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="R18" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T18" s="9" t="s">
         <v>23</v>
@@ -3531,10 +3511,10 @@
         <v>24</v>
       </c>
       <c r="V18" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W18" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="X18" s="2" t="s">
         <v>52</v>
@@ -3549,19 +3529,19 @@
         <v>9573930902</v>
       </c>
       <c r="AB18" s="8" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AC18" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD18" s="12">
         <v>44494</v>
       </c>
-      <c r="AE18" s="31" t="s">
-        <v>323</v>
-      </c>
-      <c r="AF18" s="31" t="s">
-        <v>374</v>
+      <c r="AE18" s="29" t="s">
+        <v>319</v>
+      </c>
+      <c r="AF18" s="29" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="19" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -3590,7 +3570,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J19" s="10">
         <v>1</v>
@@ -3608,16 +3588,16 @@
         <v>100</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P19" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q19" s="11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="R19" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="S19" s="4">
         <v>411229020</v>
@@ -3626,19 +3606,19 @@
         <v>23</v>
       </c>
       <c r="U19" s="9" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="V19" s="9" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="W19" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="X19" s="4" t="s">
         <v>53</v>
       </c>
       <c r="Y19" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z19" s="9">
         <v>0</v>
@@ -3647,19 +3627,19 @@
         <v>6301651210</v>
       </c>
       <c r="AB19" s="8" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AC19" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD19" s="12">
         <v>44529</v>
       </c>
-      <c r="AE19" s="31" t="s">
-        <v>324</v>
-      </c>
-      <c r="AF19" s="31" t="s">
-        <v>375</v>
+      <c r="AE19" s="29" t="s">
+        <v>320</v>
+      </c>
+      <c r="AF19" s="29" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="20" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -3688,7 +3668,7 @@
         <v>1</v>
       </c>
       <c r="I20" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J20" s="10">
         <v>1</v>
@@ -3706,16 +3686,16 @@
         <v>100</v>
       </c>
       <c r="O20" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P20" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q20" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="R20" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="S20" s="6">
         <v>500229089</v>
@@ -3727,16 +3707,16 @@
         <v>24</v>
       </c>
       <c r="V20" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W20" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="X20" s="4" t="s">
         <v>54</v>
       </c>
       <c r="Y20" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z20" s="9">
         <v>0</v>
@@ -3745,19 +3725,19 @@
         <v>9966426886</v>
       </c>
       <c r="AB20" s="8" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AC20" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD20" s="12">
         <v>44624</v>
       </c>
-      <c r="AE20" s="31" t="s">
-        <v>325</v>
-      </c>
-      <c r="AF20" s="31" t="s">
-        <v>376</v>
+      <c r="AE20" s="29" t="s">
+        <v>321</v>
+      </c>
+      <c r="AF20" s="29" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="21" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -3786,7 +3766,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="9">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="J21" s="10">
         <v>1</v>
@@ -3804,16 +3784,16 @@
         <v>100</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P21" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q21" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R21" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="S21" s="8">
         <v>500229004</v>
@@ -3825,10 +3805,10 @@
         <v>24</v>
       </c>
       <c r="V21" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W21" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="X21" s="4" t="s">
         <v>55</v>
@@ -3843,19 +3823,19 @@
         <v>9885903996</v>
       </c>
       <c r="AB21" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AC21" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD21" s="12">
         <v>44767</v>
       </c>
-      <c r="AE21" s="31" t="s">
-        <v>326</v>
-      </c>
-      <c r="AF21" s="31" t="s">
-        <v>377</v>
+      <c r="AE21" s="29" t="s">
+        <v>322</v>
+      </c>
+      <c r="AF21" s="29" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="22" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -3884,7 +3864,7 @@
         <v>1</v>
       </c>
       <c r="I22" s="9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J22" s="10">
         <v>1</v>
@@ -3902,16 +3882,16 @@
         <v>100</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P22" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q22" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R22" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="S22" s="8">
         <v>500229089</v>
@@ -3923,16 +3903,16 @@
         <v>24</v>
       </c>
       <c r="V22" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W22" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="X22" s="4" t="s">
         <v>56</v>
       </c>
       <c r="Y22" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z22" s="9">
         <v>0</v>
@@ -3941,19 +3921,19 @@
         <v>8699309990</v>
       </c>
       <c r="AB22" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AC22" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD22" s="12">
         <v>44844</v>
       </c>
-      <c r="AE22" s="31" t="s">
-        <v>327</v>
-      </c>
-      <c r="AF22" s="31" t="s">
-        <v>378</v>
+      <c r="AE22" s="29" t="s">
+        <v>323</v>
+      </c>
+      <c r="AF22" s="29" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="23" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -3982,7 +3962,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J23" s="10">
         <v>1</v>
@@ -4000,16 +3980,16 @@
         <v>100</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P23" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q23" s="20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="R23" s="19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S23" s="19">
         <v>500002168</v>
@@ -4021,10 +4001,10 @@
         <v>24</v>
       </c>
       <c r="V23" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W23" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="X23" s="4" t="s">
         <v>57</v>
@@ -4039,19 +4019,19 @@
         <v>9866177082</v>
       </c>
       <c r="AB23" s="8" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AC23" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD23" s="12">
         <v>44844</v>
       </c>
-      <c r="AE23" s="31" t="s">
-        <v>328</v>
-      </c>
-      <c r="AF23" s="31" t="s">
-        <v>379</v>
+      <c r="AE23" s="29" t="s">
+        <v>324</v>
+      </c>
+      <c r="AF23" s="29" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="24" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -4080,7 +4060,7 @@
         <v>1</v>
       </c>
       <c r="I24" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J24" s="10">
         <v>1</v>
@@ -4098,16 +4078,16 @@
         <v>100</v>
       </c>
       <c r="O24" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P24" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q24" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="R24" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="S24" s="8">
         <v>500229034</v>
@@ -4122,13 +4102,13 @@
         <v>25</v>
       </c>
       <c r="W24" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="X24" s="4" t="s">
         <v>58</v>
       </c>
       <c r="Y24" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z24" s="9">
         <v>0</v>
@@ -4137,19 +4117,19 @@
         <v>9966473904</v>
       </c>
       <c r="AB24" s="8" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AC24" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD24" s="12">
         <v>44929</v>
       </c>
-      <c r="AE24" s="31" t="s">
-        <v>329</v>
-      </c>
-      <c r="AF24" s="31" t="s">
-        <v>380</v>
+      <c r="AE24" s="29" t="s">
+        <v>325</v>
+      </c>
+      <c r="AF24" s="29" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="25" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -4178,7 +4158,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J25" s="10">
         <v>1</v>
@@ -4196,16 +4176,16 @@
         <v>100</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P25" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q25" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="R25" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="S25" s="8">
         <v>500002011</v>
@@ -4217,16 +4197,16 @@
         <v>24</v>
       </c>
       <c r="V25" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W25" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="X25" s="4" t="s">
         <v>59</v>
       </c>
       <c r="Y25" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z25" s="9">
         <v>0</v>
@@ -4235,19 +4215,19 @@
         <v>9493532937</v>
       </c>
       <c r="AB25" s="8" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AC25" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD25" s="12">
         <v>44929</v>
       </c>
-      <c r="AE25" s="31" t="s">
-        <v>330</v>
-      </c>
-      <c r="AF25" s="31" t="s">
-        <v>381</v>
+      <c r="AE25" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="AF25" s="29" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="26" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -4276,7 +4256,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J26" s="10">
         <v>1</v>
@@ -4294,16 +4274,16 @@
         <v>100</v>
       </c>
       <c r="O26" s="9" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q26" s="16" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="R26" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="S26" s="17">
         <v>530240022</v>
@@ -4312,10 +4292,10 @@
         <v>23</v>
       </c>
       <c r="U26" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="W26" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="X26" s="4" t="s">
         <v>60</v>
@@ -4330,19 +4310,19 @@
         <v>9676047345</v>
       </c>
       <c r="AB26" s="8" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AC26" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD26" s="12">
         <v>44935</v>
       </c>
-      <c r="AE26" s="31" t="s">
-        <v>331</v>
-      </c>
-      <c r="AF26" s="31" t="s">
-        <v>382</v>
+      <c r="AE26" s="29" t="s">
+        <v>327</v>
+      </c>
+      <c r="AF26" s="29" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="27" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -4371,7 +4351,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="10">
         <v>1</v>
@@ -4389,31 +4369,31 @@
         <v>100</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P27" s="17" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q27" s="16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R27" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="S27" s="17" t="s">
         <v>112</v>
-      </c>
-      <c r="S27" s="17" t="s">
-        <v>113</v>
       </c>
       <c r="T27" s="9" t="s">
         <v>23</v>
       </c>
       <c r="U27" s="9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V27" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="W27" s="17" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="X27" s="4" t="s">
         <v>61</v>
@@ -4428,19 +4408,19 @@
         <v>7794084333</v>
       </c>
       <c r="AB27" s="8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AC27" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD27" s="12">
         <v>44980</v>
       </c>
-      <c r="AE27" s="31" t="s">
-        <v>276</v>
-      </c>
-      <c r="AF27" s="31" t="s">
-        <v>383</v>
+      <c r="AE27" s="29" t="s">
+        <v>274</v>
+      </c>
+      <c r="AF27" s="29" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="28" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -4469,7 +4449,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J28" s="10">
         <v>1</v>
@@ -4487,16 +4467,16 @@
         <v>100</v>
       </c>
       <c r="O28" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P28" s="17" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q28" s="16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R28" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="S28" s="17">
         <v>523229002</v>
@@ -4505,13 +4485,13 @@
         <v>23</v>
       </c>
       <c r="U28" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="V28" s="9" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="W28" s="17" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="X28" s="4" t="s">
         <v>62</v>
@@ -4526,19 +4506,19 @@
         <v>9390690999</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AC28" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD28" s="12">
         <v>44986</v>
       </c>
-      <c r="AE28" s="31" t="s">
-        <v>332</v>
-      </c>
-      <c r="AF28" s="31" t="s">
-        <v>384</v>
+      <c r="AE28" s="29" t="s">
+        <v>328</v>
+      </c>
+      <c r="AF28" s="29" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="29" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -4558,7 +4538,7 @@
         <v>2</v>
       </c>
       <c r="F29" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G29" s="10">
         <v>1</v>
@@ -4567,7 +4547,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J29" s="10">
         <v>1</v>
@@ -4585,16 +4565,16 @@
         <v>100</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P29" s="21" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q29" s="22" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="R29" s="21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="S29" s="21">
         <v>500229002</v>
@@ -4606,10 +4586,10 @@
         <v>24</v>
       </c>
       <c r="V29" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W29" s="21" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="X29" s="21" t="s">
         <v>63</v>
@@ -4624,19 +4604,19 @@
         <v>9966881111</v>
       </c>
       <c r="AB29" s="21" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AC29" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD29" s="23">
         <v>45078</v>
       </c>
-      <c r="AE29" s="31" t="s">
-        <v>333</v>
-      </c>
-      <c r="AF29" s="31" t="s">
-        <v>385</v>
+      <c r="AE29" s="29" t="s">
+        <v>329</v>
+      </c>
+      <c r="AF29" s="29" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="30" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -4665,7 +4645,7 @@
         <v>1</v>
       </c>
       <c r="I30" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="10">
         <v>1</v>
@@ -4683,31 +4663,31 @@
         <v>100</v>
       </c>
       <c r="O30" s="9" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P30" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q30" s="14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R30" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="S30" s="10" t="s">
         <v>116</v>
-      </c>
-      <c r="S30" s="10" t="s">
-        <v>117</v>
       </c>
       <c r="T30" s="9" t="s">
         <v>23</v>
       </c>
       <c r="U30" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="V30" s="9" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="W30" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="X30" s="6" t="s">
         <v>64</v>
@@ -4722,19 +4702,19 @@
         <v>6300100871</v>
       </c>
       <c r="AB30" s="9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AC30" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD30" s="25">
         <v>45096</v>
       </c>
-      <c r="AE30" s="31" t="s">
-        <v>334</v>
-      </c>
-      <c r="AF30" s="31" t="s">
-        <v>386</v>
+      <c r="AE30" s="29" t="s">
+        <v>330</v>
+      </c>
+      <c r="AF30" s="29" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="31" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -4763,7 +4743,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J31" s="10">
         <v>1</v>
@@ -4781,16 +4761,16 @@
         <v>100</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q31" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R31" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="S31" s="6">
         <v>600229021</v>
@@ -4799,13 +4779,13 @@
         <v>23</v>
       </c>
       <c r="U31" s="9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="V31" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="W31" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X31" s="6" t="s">
         <v>35</v>
@@ -4820,19 +4800,19 @@
         <v>8885603384</v>
       </c>
       <c r="AB31" s="9" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AC31" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD31" s="25">
         <v>45103</v>
       </c>
-      <c r="AE31" s="31" t="s">
-        <v>335</v>
-      </c>
-      <c r="AF31" s="31" t="s">
-        <v>387</v>
+      <c r="AE31" s="29" t="s">
+        <v>331</v>
+      </c>
+      <c r="AF31" s="29" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="32" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -4861,7 +4841,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J32" s="10">
         <v>1</v>
@@ -4879,16 +4859,16 @@
         <v>100</v>
       </c>
       <c r="O32" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P32" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q32" s="14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R32" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S32" s="10">
         <v>500229016</v>
@@ -4900,16 +4880,16 @@
         <v>24</v>
       </c>
       <c r="V32" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W32" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="X32" s="4" t="s">
         <v>65</v>
       </c>
       <c r="Y32" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z32" s="9">
         <v>0</v>
@@ -4918,19 +4898,19 @@
         <v>9676534919</v>
       </c>
       <c r="AB32" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AC32" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD32" s="25">
         <v>45231</v>
       </c>
-      <c r="AE32" s="31" t="s">
-        <v>336</v>
-      </c>
-      <c r="AF32" s="31" t="s">
-        <v>388</v>
+      <c r="AE32" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="AF32" s="29" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="33" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -4959,7 +4939,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J33" s="10">
         <v>1</v>
@@ -4977,16 +4957,16 @@
         <v>100</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q33" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="R33" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="S33" s="4">
         <v>504229202</v>
@@ -4995,13 +4975,13 @@
         <v>23</v>
       </c>
       <c r="U33" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="V33" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="W33" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="X33" s="4" t="s">
         <v>66</v>
@@ -5016,19 +4996,19 @@
         <v>8074718217</v>
       </c>
       <c r="AB33" s="8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AC33" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD33" s="12">
         <v>45246</v>
       </c>
-      <c r="AE33" s="31" t="s">
-        <v>337</v>
-      </c>
-      <c r="AF33" s="31" t="s">
-        <v>389</v>
+      <c r="AE33" s="29" t="s">
+        <v>333</v>
+      </c>
+      <c r="AF33" s="29" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="34" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -5057,7 +5037,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J34" s="10">
         <v>1</v>
@@ -5075,19 +5055,19 @@
         <v>100</v>
       </c>
       <c r="O34" s="9" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P34" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q34" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="R34" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="S34" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="S34" s="10" t="s">
-        <v>122</v>
       </c>
       <c r="T34" s="9" t="s">
         <v>23</v>
@@ -5096,10 +5076,10 @@
         <v>24</v>
       </c>
       <c r="V34" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W34" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="X34" s="4" t="s">
         <v>67</v>
@@ -5114,19 +5094,19 @@
         <v>8555045682</v>
       </c>
       <c r="AB34" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AC34" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD34" s="12">
         <v>45293</v>
       </c>
-      <c r="AE34" s="31" t="s">
-        <v>338</v>
-      </c>
-      <c r="AF34" s="31" t="s">
-        <v>390</v>
+      <c r="AE34" s="29" t="s">
+        <v>334</v>
+      </c>
+      <c r="AF34" s="29" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="35" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -5155,7 +5135,7 @@
         <v>1</v>
       </c>
       <c r="I35" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J35" s="10">
         <v>1</v>
@@ -5173,16 +5153,16 @@
         <v>100</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q35" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="R35" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="S35" s="4">
         <v>500229003</v>
@@ -5194,10 +5174,10 @@
         <v>24</v>
       </c>
       <c r="V35" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W35" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="X35" s="4" t="s">
         <v>68</v>
@@ -5212,19 +5192,19 @@
         <v>9000400733</v>
       </c>
       <c r="AB35" s="8" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AC35" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD35" s="12">
         <v>45329</v>
       </c>
-      <c r="AE35" s="31" t="s">
-        <v>339</v>
-      </c>
-      <c r="AF35" s="31" t="s">
-        <v>391</v>
+      <c r="AE35" s="29" t="s">
+        <v>335</v>
+      </c>
+      <c r="AF35" s="29" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="36" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -5253,7 +5233,7 @@
         <v>1</v>
       </c>
       <c r="I36" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J36" s="10">
         <v>1</v>
@@ -5271,31 +5251,31 @@
         <v>100</v>
       </c>
       <c r="O36" s="9" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P36" s="17" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="Q36" s="16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="R36" s="17" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="S36" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="T36" s="9" t="s">
         <v>23</v>
       </c>
       <c r="U36" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="V36" s="9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="W36" s="17" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="X36" s="4" t="s">
         <v>69</v>
@@ -5310,19 +5290,19 @@
         <v>9398598157</v>
       </c>
       <c r="AB36" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AC36" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD36" s="12">
         <v>45362</v>
       </c>
-      <c r="AE36" s="31" t="s">
-        <v>340</v>
-      </c>
-      <c r="AF36" s="31" t="s">
-        <v>392</v>
+      <c r="AE36" s="29" t="s">
+        <v>336</v>
+      </c>
+      <c r="AF36" s="29" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="37" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -5351,7 +5331,7 @@
         <v>1</v>
       </c>
       <c r="I37" s="9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J37" s="10">
         <v>1</v>
@@ -5369,16 +5349,16 @@
         <v>100</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P37" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q37" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="R37" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="S37" s="9">
         <v>500240075</v>
@@ -5390,10 +5370,10 @@
         <v>24</v>
       </c>
       <c r="V37" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W37" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="X37" s="4" t="s">
         <v>70</v>
@@ -5408,19 +5388,19 @@
         <v>8106848962</v>
       </c>
       <c r="AB37" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AC37" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD37" s="12">
         <v>45390</v>
       </c>
-      <c r="AE37" s="31" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF37" s="31" t="s">
-        <v>393</v>
+      <c r="AE37" s="29" t="s">
+        <v>337</v>
+      </c>
+      <c r="AF37" s="29" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="38" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -5440,7 +5420,7 @@
         <v>5</v>
       </c>
       <c r="F38" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G38" s="10">
         <v>1</v>
@@ -5449,7 +5429,7 @@
         <v>1</v>
       </c>
       <c r="I38" s="9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J38" s="10">
         <v>1</v>
@@ -5467,16 +5447,16 @@
         <v>100</v>
       </c>
       <c r="O38" s="9" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P38" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q38" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R38" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="S38" s="6">
         <v>500240096</v>
@@ -5488,10 +5468,10 @@
         <v>24</v>
       </c>
       <c r="V38" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W38" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="X38" s="4" t="s">
         <v>71</v>
@@ -5506,19 +5486,19 @@
         <v>8985370398</v>
       </c>
       <c r="AB38" s="8" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AC38" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD38" s="12">
         <v>45413</v>
       </c>
-      <c r="AE38" s="31" t="s">
-        <v>342</v>
-      </c>
-      <c r="AF38" s="31" t="s">
-        <v>394</v>
+      <c r="AE38" s="29" t="s">
+        <v>338</v>
+      </c>
+      <c r="AF38" s="29" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="39" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -5547,7 +5527,7 @@
         <v>1</v>
       </c>
       <c r="I39" s="9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J39" s="10">
         <v>1</v>
@@ -5565,16 +5545,16 @@
         <v>100</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P39" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q39" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R39" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="S39" s="9">
         <v>535211002</v>
@@ -5583,19 +5563,19 @@
         <v>23</v>
       </c>
       <c r="U39" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="V39" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="W39" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="X39" s="4" t="s">
         <v>72</v>
       </c>
       <c r="Y39" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z39" s="9">
         <v>0</v>
@@ -5604,19 +5584,19 @@
         <v>8341256156</v>
       </c>
       <c r="AB39" s="8" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="AC39" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD39" s="12">
         <v>45457</v>
       </c>
-      <c r="AE39" s="31" t="s">
-        <v>343</v>
-      </c>
-      <c r="AF39" s="31" t="s">
-        <v>395</v>
+      <c r="AE39" s="29" t="s">
+        <v>339</v>
+      </c>
+      <c r="AF39" s="29" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="40" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -5645,7 +5625,7 @@
         <v>1</v>
       </c>
       <c r="I40" s="9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J40" s="10">
         <v>1</v>
@@ -5663,16 +5643,16 @@
         <v>100</v>
       </c>
       <c r="O40" s="9" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P40" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q40" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="R40" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S40" s="9">
         <v>843211003</v>
@@ -5681,19 +5661,19 @@
         <v>23</v>
       </c>
       <c r="U40" s="9" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="V40" s="9" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="W40" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="X40" s="4" t="s">
         <v>73</v>
       </c>
       <c r="Y40" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z40" s="9">
         <v>0</v>
@@ -5702,19 +5682,19 @@
         <v>7411608393</v>
       </c>
       <c r="AB40" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="AC40" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD40" s="12">
         <v>45481</v>
       </c>
-      <c r="AE40" s="31" t="s">
-        <v>344</v>
-      </c>
-      <c r="AF40" s="31" t="s">
-        <v>396</v>
+      <c r="AE40" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AF40" s="29" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="41" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -5743,7 +5723,7 @@
         <v>1</v>
       </c>
       <c r="I41" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J41" s="10">
         <v>1</v>
@@ -5761,16 +5741,16 @@
         <v>100</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P41" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q41" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="R41" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="S41" s="9">
         <v>530002308</v>
@@ -5779,19 +5759,19 @@
         <v>23</v>
       </c>
       <c r="U41" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="V41" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="W41" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="X41" s="4" t="s">
         <v>74</v>
       </c>
       <c r="Y41" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z41" s="9">
         <v>0</v>
@@ -5800,19 +5780,19 @@
         <v>9963762979</v>
       </c>
       <c r="AB41" s="8" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AC41" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD41" s="12">
         <v>45484</v>
       </c>
-      <c r="AE41" s="31" t="s">
-        <v>345</v>
-      </c>
-      <c r="AF41" s="31" t="s">
-        <v>397</v>
+      <c r="AE41" s="29" t="s">
+        <v>341</v>
+      </c>
+      <c r="AF41" s="29" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="42" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -5841,7 +5821,7 @@
         <v>1</v>
       </c>
       <c r="I42" s="9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J42" s="10">
         <v>1</v>
@@ -5859,16 +5839,16 @@
         <v>100</v>
       </c>
       <c r="O42" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P42" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q42" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="R42" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="S42" s="6">
         <v>523229602</v>
@@ -5877,13 +5857,13 @@
         <v>23</v>
       </c>
       <c r="U42" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="V42" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="W42" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="X42" s="4" t="s">
         <v>75</v>
@@ -5898,19 +5878,19 @@
         <v>9701276764</v>
       </c>
       <c r="AB42" s="8" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AC42" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD42" s="12">
         <v>45502</v>
       </c>
-      <c r="AE42" s="31" t="s">
-        <v>276</v>
-      </c>
-      <c r="AF42" s="31" t="s">
-        <v>398</v>
+      <c r="AE42" s="29" t="s">
+        <v>274</v>
+      </c>
+      <c r="AF42" s="29" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="43" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -5939,7 +5919,7 @@
         <v>1</v>
       </c>
       <c r="I43" s="9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J43" s="10">
         <v>1</v>
@@ -5957,19 +5937,19 @@
         <v>100</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q43" s="14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="R43" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="S43" s="8" t="s">
         <v>130</v>
-      </c>
-      <c r="S43" s="8" t="s">
-        <v>131</v>
       </c>
       <c r="T43" s="9" t="s">
         <v>23</v>
@@ -5978,16 +5958,16 @@
         <v>24</v>
       </c>
       <c r="V43" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W43" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="X43" s="4" t="s">
         <v>76</v>
       </c>
       <c r="Y43" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z43" s="9">
         <v>0</v>
@@ -5996,19 +5976,19 @@
         <v>9966777535</v>
       </c>
       <c r="AB43" s="8" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AC43" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD43" s="12">
         <v>45537</v>
       </c>
-      <c r="AE43" s="31" t="s">
-        <v>346</v>
-      </c>
-      <c r="AF43" s="31" t="s">
-        <v>399</v>
+      <c r="AE43" s="29" t="s">
+        <v>342</v>
+      </c>
+      <c r="AF43" s="29" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="44" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -6037,7 +6017,7 @@
         <v>1</v>
       </c>
       <c r="I44" s="9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J44" s="10">
         <v>1</v>
@@ -6055,19 +6035,19 @@
         <v>100</v>
       </c>
       <c r="O44" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P44" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q44" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="R44" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="S44" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="T44" s="9" t="s">
         <v>23</v>
@@ -6076,16 +6056,16 @@
         <v>24</v>
       </c>
       <c r="V44" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W44" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="X44" s="4" t="s">
         <v>77</v>
       </c>
       <c r="Y44" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z44" s="9">
         <v>0</v>
@@ -6094,19 +6074,19 @@
         <v>8500416093</v>
       </c>
       <c r="AB44" s="9" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AC44" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD44" s="12">
         <v>45581</v>
       </c>
-      <c r="AE44" s="31" t="s">
-        <v>347</v>
-      </c>
-      <c r="AF44" s="31" t="s">
-        <v>384</v>
+      <c r="AE44" s="29" t="s">
+        <v>343</v>
+      </c>
+      <c r="AF44" s="29" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="45" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -6135,7 +6115,7 @@
         <v>1</v>
       </c>
       <c r="I45" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J45" s="10">
         <v>1</v>
@@ -6153,16 +6133,16 @@
         <v>100</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q45" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="R45" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="S45" s="8">
         <v>500229092</v>
@@ -6174,16 +6154,16 @@
         <v>24</v>
       </c>
       <c r="V45" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W45" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="X45" s="29" t="s">
+        <v>220</v>
+      </c>
+      <c r="X45" s="28" t="s">
         <v>78</v>
       </c>
       <c r="Y45" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z45" s="9">
         <v>0</v>
@@ -6192,19 +6172,19 @@
         <v>9849992969</v>
       </c>
       <c r="AB45" s="9" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AC45" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD45" s="12">
         <v>45581</v>
       </c>
-      <c r="AE45" s="31" t="s">
-        <v>308</v>
-      </c>
-      <c r="AF45" s="31" t="s">
-        <v>400</v>
+      <c r="AE45" s="29" t="s">
+        <v>304</v>
+      </c>
+      <c r="AF45" s="29" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="46" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
@@ -6233,7 +6213,7 @@
         <v>1</v>
       </c>
       <c r="I46" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J46" s="10">
         <v>1</v>
@@ -6251,16 +6231,16 @@
         <v>100</v>
       </c>
       <c r="O46" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P46" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q46" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="R46" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="S46" s="8">
         <v>500229092</v>
@@ -6272,16 +6252,16 @@
         <v>24</v>
       </c>
       <c r="V46" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W46" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="X46" s="4" t="s">
         <v>79</v>
       </c>
       <c r="Y46" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z46" s="9">
         <v>0</v>
@@ -6290,30 +6270,30 @@
         <v>9848782727</v>
       </c>
       <c r="AB46" s="8" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AC46" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD46" s="12">
         <v>45581</v>
       </c>
-      <c r="AE46" s="31" t="s">
-        <v>348</v>
-      </c>
-      <c r="AF46" s="31" t="s">
-        <v>401</v>
+      <c r="AE46" s="29" t="s">
+        <v>344</v>
+      </c>
+      <c r="AF46" s="29" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="47" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A47" s="8">
-        <v>16150</v>
+        <v>16151</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C47" s="8">
-        <v>8331904575</v>
+      <c r="C47" s="9">
+        <v>9573357536</v>
       </c>
       <c r="D47" s="9">
         <v>1</v>
@@ -6331,7 +6311,7 @@
         <v>1</v>
       </c>
       <c r="I47" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J47" s="10">
         <v>1</v>
@@ -6349,19 +6329,19 @@
         <v>100</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="P47" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q47" s="26">
-        <v>50100209612362</v>
-      </c>
-      <c r="R47" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="S47" s="9">
-        <v>500240025</v>
+        <v>225</v>
+      </c>
+      <c r="P47" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q47" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="R47" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="S47" s="8" t="s">
+        <v>130</v>
       </c>
       <c r="T47" s="9" t="s">
         <v>23</v>
@@ -6370,48 +6350,48 @@
         <v>24</v>
       </c>
       <c r="V47" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="W47" s="9" t="s">
-        <v>222</v>
+        <v>234</v>
+      </c>
+      <c r="W47" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="X47" s="4" t="s">
         <v>80</v>
       </c>
       <c r="Y47" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z47" s="9">
         <v>0</v>
       </c>
-      <c r="AA47" s="9">
-        <v>9490792089</v>
-      </c>
-      <c r="AB47" s="9" t="s">
-        <v>295</v>
+      <c r="AA47" s="8">
+        <v>9866218721</v>
+      </c>
+      <c r="AB47" s="8" t="s">
+        <v>293</v>
       </c>
       <c r="AC47" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD47" s="12">
         <v>45581</v>
       </c>
-      <c r="AE47" s="31" t="s">
-        <v>349</v>
-      </c>
-      <c r="AF47" s="31" t="s">
-        <v>402</v>
+      <c r="AE47" s="29" t="s">
+        <v>345</v>
+      </c>
+      <c r="AF47" s="29" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="48" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A48" s="8">
-        <v>16151</v>
+        <v>16152</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>81</v>
       </c>
       <c r="C48" s="9">
-        <v>9573357536</v>
+        <v>9818921487</v>
       </c>
       <c r="D48" s="9">
         <v>1</v>
@@ -6429,7 +6409,7 @@
         <v>1</v>
       </c>
       <c r="I48" s="9">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="J48" s="10">
         <v>1</v>
@@ -6447,69 +6427,69 @@
         <v>100</v>
       </c>
       <c r="O48" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P48" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q48" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="R48" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q48" s="8">
+        <v>3747990559</v>
+      </c>
+      <c r="R48" s="9" t="s">
         <v>134</v>
       </c>
       <c r="S48" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="T48" s="9" t="s">
         <v>23</v>
       </c>
       <c r="U48" s="9" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="V48" s="9" t="s">
-        <v>236</v>
+        <v>87</v>
       </c>
       <c r="W48" s="8" t="s">
-        <v>25</v>
+        <v>221</v>
       </c>
       <c r="X48" s="4" t="s">
         <v>81</v>
       </c>
       <c r="Y48" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z48" s="9">
         <v>0</v>
       </c>
       <c r="AA48" s="8">
-        <v>9866218721</v>
+        <v>7759821545</v>
       </c>
       <c r="AB48" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AC48" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD48" s="12">
         <v>45581</v>
       </c>
-      <c r="AE48" s="31" t="s">
-        <v>350</v>
-      </c>
-      <c r="AF48" s="31" t="s">
-        <v>403</v>
+      <c r="AE48" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AF48" s="29" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="49" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A49" s="8">
-        <v>16152</v>
+        <v>16153</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>82</v>
       </c>
       <c r="C49" s="9">
-        <v>9818921487</v>
+        <v>6302090336</v>
       </c>
       <c r="D49" s="9">
         <v>1</v>
@@ -6527,7 +6507,7 @@
         <v>1</v>
       </c>
       <c r="I49" s="9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J49" s="10">
         <v>1</v>
@@ -6545,69 +6525,69 @@
         <v>100</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="P49" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q49" s="8">
-        <v>3747990559</v>
-      </c>
-      <c r="R49" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="S49" s="8" t="s">
-        <v>131</v>
+        <v>224</v>
+      </c>
+      <c r="P49" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q49" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="R49" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="S49" s="8">
+        <v>500229092</v>
       </c>
       <c r="T49" s="9" t="s">
         <v>23</v>
       </c>
       <c r="U49" s="9" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="V49" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="W49" s="8" t="s">
-        <v>223</v>
+        <v>234</v>
+      </c>
+      <c r="W49" s="9" t="s">
+        <v>220</v>
       </c>
       <c r="X49" s="4" t="s">
         <v>82</v>
       </c>
       <c r="Y49" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z49" s="9">
         <v>0</v>
       </c>
       <c r="AA49" s="8">
-        <v>7759821545</v>
+        <v>7671020860</v>
       </c>
       <c r="AB49" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AC49" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD49" s="12">
         <v>45581</v>
       </c>
-      <c r="AE49" s="31" t="s">
-        <v>351</v>
-      </c>
-      <c r="AF49" s="31" t="s">
-        <v>404</v>
+      <c r="AE49" s="29" t="s">
+        <v>347</v>
+      </c>
+      <c r="AF49" s="29" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="50" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A50" s="8">
-        <v>16153</v>
+        <v>16154</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C50" s="9">
-        <v>6302090336</v>
+      <c r="C50" s="8">
+        <v>9030884974</v>
       </c>
       <c r="D50" s="9">
         <v>1</v>
@@ -6625,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="I50" s="9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J50" s="10">
         <v>1</v>
@@ -6643,16 +6623,16 @@
         <v>100</v>
       </c>
       <c r="O50" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P50" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q50" s="11" t="s">
         <v>184</v>
       </c>
       <c r="R50" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="S50" s="8">
         <v>500229092</v>
@@ -6664,54 +6644,54 @@
         <v>24</v>
       </c>
       <c r="V50" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W50" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="X50" s="4" t="s">
         <v>83</v>
       </c>
       <c r="Y50" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Z50" s="9">
         <v>0</v>
       </c>
-      <c r="AA50" s="8">
-        <v>7671020860</v>
+      <c r="AA50" s="9">
+        <v>6281216376</v>
       </c>
       <c r="AB50" s="8" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AC50" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD50" s="12">
         <v>45581</v>
       </c>
-      <c r="AE50" s="31" t="s">
-        <v>352</v>
-      </c>
-      <c r="AF50" s="31" t="s">
-        <v>405</v>
+      <c r="AE50" s="29" t="s">
+        <v>348</v>
+      </c>
+      <c r="AF50" s="29" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="51" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A51" s="8">
-        <v>16154</v>
+        <v>16155</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C51" s="8">
-        <v>9030884974</v>
+        <v>8121125383</v>
       </c>
       <c r="D51" s="9">
         <v>1</v>
       </c>
       <c r="E51" s="8">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F51" s="9">
         <v>7</v>
@@ -6723,7 +6703,7 @@
         <v>1</v>
       </c>
       <c r="I51" s="9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J51" s="10">
         <v>1</v>
@@ -6741,19 +6721,19 @@
         <v>100</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="P51" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q51" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="P51" s="26" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q51" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="R51" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="S51" s="8">
-        <v>500229092</v>
+      <c r="R51" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="S51" s="26" t="s">
+        <v>130</v>
       </c>
       <c r="T51" s="9" t="s">
         <v>23</v>
@@ -6762,54 +6742,54 @@
         <v>24</v>
       </c>
       <c r="V51" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="W51" s="9" t="s">
-        <v>221</v>
+        <v>234</v>
+      </c>
+      <c r="W51" s="26" t="s">
+        <v>222</v>
       </c>
       <c r="X51" s="4" t="s">
         <v>84</v>
       </c>
       <c r="Y51" s="8" t="s">
-        <v>249</v>
+        <v>29</v>
       </c>
       <c r="Z51" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA51" s="9">
-        <v>6281216376</v>
+        <v>2</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>7075815850</v>
       </c>
       <c r="AB51" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AC51" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD51" s="12">
-        <v>45581</v>
-      </c>
-      <c r="AE51" s="31" t="s">
-        <v>353</v>
-      </c>
-      <c r="AF51" s="31" t="s">
-        <v>406</v>
+        <v>45642</v>
+      </c>
+      <c r="AE51" s="29" t="s">
+        <v>349</v>
+      </c>
+      <c r="AF51" s="29" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="52" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A52" s="8">
-        <v>16155</v>
+        <v>16156</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>85</v>
       </c>
       <c r="C52" s="8">
-        <v>8121125383</v>
+        <v>9090260187</v>
       </c>
       <c r="D52" s="9">
         <v>1</v>
       </c>
       <c r="E52" s="8">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F52" s="9">
         <v>7</v>
@@ -6821,7 +6801,7 @@
         <v>1</v>
       </c>
       <c r="I52" s="9">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="J52" s="10">
         <v>1</v>
@@ -6830,7 +6810,7 @@
         <v>1</v>
       </c>
       <c r="L52" s="9" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="M52" s="9">
         <v>100000</v>
@@ -6841,29 +6821,29 @@
       <c r="O52" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="P52" s="27" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q52" s="28" t="s">
+      <c r="P52" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q52" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="R52" s="27" t="s">
+      <c r="R52" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="S52" s="27" t="s">
-        <v>131</v>
+      <c r="S52" s="26">
+        <v>751211008</v>
       </c>
       <c r="T52" s="9" t="s">
         <v>23</v>
       </c>
       <c r="U52" s="9" t="s">
-        <v>24</v>
+        <v>244</v>
       </c>
       <c r="V52" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="W52" s="27" t="s">
-        <v>224</v>
+        <v>88</v>
+      </c>
+      <c r="W52" s="26" t="s">
+        <v>223</v>
       </c>
       <c r="X52" s="4" t="s">
         <v>85</v>
@@ -6872,36 +6852,36 @@
         <v>29</v>
       </c>
       <c r="Z52" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA52" s="8">
-        <v>7075815850</v>
+        <v>9740911943</v>
       </c>
       <c r="AB52" s="8" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="AC52" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD52" s="12">
-        <v>45642</v>
-      </c>
-      <c r="AE52" s="31" t="s">
-        <v>354</v>
-      </c>
-      <c r="AF52" s="31" t="s">
-        <v>407</v>
+        <v>45677</v>
+      </c>
+      <c r="AE52" s="29" t="s">
+        <v>350</v>
+      </c>
+      <c r="AF52" s="29" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="53" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A53" s="8">
-        <v>16156</v>
+        <v>16157</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C53" s="8">
-        <v>9090260187</v>
+        <v>7859862330</v>
       </c>
       <c r="D53" s="9">
         <v>1</v>
@@ -6919,7 +6899,7 @@
         <v>1</v>
       </c>
       <c r="I53" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J53" s="10">
         <v>1</v>
@@ -6928,7 +6908,7 @@
         <v>1</v>
       </c>
       <c r="L53" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M53" s="9">
         <v>100000</v>
@@ -6937,160 +6917,62 @@
         <v>100</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="P53" s="27" t="s">
-        <v>225</v>
-      </c>
-      <c r="Q53" s="28" t="s">
-        <v>187</v>
-      </c>
-      <c r="R53" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="S53" s="27">
-        <v>751211008</v>
+        <v>130</v>
+      </c>
+      <c r="P53" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q53" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="R53" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="S53" s="9" t="s">
+        <v>130</v>
       </c>
       <c r="T53" s="9" t="s">
         <v>23</v>
       </c>
       <c r="U53" s="9" t="s">
-        <v>246</v>
+        <v>87</v>
       </c>
       <c r="V53" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="W53" s="27" t="s">
-        <v>225</v>
+        <v>245</v>
+      </c>
+      <c r="W53" s="8" t="s">
+        <v>130</v>
       </c>
       <c r="X53" s="4" t="s">
         <v>86</v>
       </c>
       <c r="Y53" s="8" t="s">
-        <v>29</v>
+        <v>247</v>
       </c>
       <c r="Z53" s="9">
         <v>0</v>
       </c>
       <c r="AA53" s="8">
-        <v>9740911943</v>
+        <v>7042944844</v>
       </c>
       <c r="AB53" s="8" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AC53" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AD53" s="12">
-        <v>45677</v>
-      </c>
-      <c r="AE53" s="31" t="s">
-        <v>355</v>
-      </c>
-      <c r="AF53" s="31" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="54" spans="1:32" s="9" customFormat="1" ht="15" customHeight="1">
-      <c r="A54" s="8">
-        <v>16157</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C54" s="8">
-        <v>7859862330</v>
-      </c>
-      <c r="D54" s="9">
-        <v>1</v>
-      </c>
-      <c r="E54" s="8">
-        <v>12</v>
-      </c>
-      <c r="F54" s="9">
-        <v>7</v>
-      </c>
-      <c r="G54" s="10">
-        <v>1</v>
-      </c>
-      <c r="H54" s="10">
-        <v>1</v>
-      </c>
-      <c r="I54" s="9">
-        <v>54</v>
-      </c>
-      <c r="J54" s="10">
-        <v>1</v>
-      </c>
-      <c r="K54" s="10">
-        <v>1</v>
-      </c>
-      <c r="L54" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M54" s="9">
-        <v>100000</v>
-      </c>
-      <c r="N54" s="9">
-        <v>100</v>
-      </c>
-      <c r="O54" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="P54" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q54" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="R54" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="S54" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="T54" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="U54" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="V54" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="W54" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="X54" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y54" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="Z54" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA54" s="8">
-        <v>7042944844</v>
-      </c>
-      <c r="AB54" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="AC54" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="AD54" s="12">
         <v>45691</v>
       </c>
-      <c r="AE54" s="31" t="s">
-        <v>356</v>
-      </c>
-      <c r="AF54" s="31" t="s">
-        <v>409</v>
+      <c r="AE53" s="29" t="s">
+        <v>351</v>
+      </c>
+      <c r="AF53" s="29" t="s">
+        <v>402</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AD54"/>
+  <autoFilter ref="A1:AD53"/>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1"/>
     <hyperlink ref="B5" r:id="rId2"/>
@@ -7141,69 +7023,67 @@
     <hyperlink ref="B51" r:id="rId47"/>
     <hyperlink ref="B52" r:id="rId48"/>
     <hyperlink ref="B53" r:id="rId49"/>
-    <hyperlink ref="B54" r:id="rId50"/>
-    <hyperlink ref="S8" r:id="rId51" display="https://micr.bankifsccode.com/520229005"/>
-    <hyperlink ref="S9" r:id="rId52" display="https://micr.bankifsccode.com/560229030"/>
-    <hyperlink ref="S19" r:id="rId53" display="https://micr.bankifsccode.com/411229020"/>
-    <hyperlink ref="S20" r:id="rId54" display="https://micr.bankifsccode.com/500229089"/>
-    <hyperlink ref="S31" r:id="rId55" display="https://micr.bankifsccode.com/600229021"/>
-    <hyperlink ref="S33" r:id="rId56" display="https://micr.bankifsccode.com/504229202"/>
-    <hyperlink ref="S35" r:id="rId57" display="https://micr.bankifsccode.com/500229003"/>
-    <hyperlink ref="S42" r:id="rId58" display="https://micr.bankifsccode.com/523229602"/>
-    <hyperlink ref="P9" r:id="rId59" display="https://bankifsccode.com/ICICI_BANK_LTD/KARNATAKA/BANGALORE_URBAN/BANGALORE_-_SARJAPUR_ROAD"/>
-    <hyperlink ref="W9" r:id="rId60" display="https://bankifsccode.com/ICICI_BANK_LTD/KARNATAKA/BANGALORE_URBAN/BANGALORE_-_SARJAPUR_ROAD"/>
-    <hyperlink ref="X2" r:id="rId61"/>
-    <hyperlink ref="X5" r:id="rId62"/>
-    <hyperlink ref="X6" r:id="rId63"/>
-    <hyperlink ref="X7" r:id="rId64"/>
-    <hyperlink ref="X8" r:id="rId65"/>
-    <hyperlink ref="X9" r:id="rId66"/>
-    <hyperlink ref="X10" r:id="rId67"/>
-    <hyperlink ref="X11" r:id="rId68"/>
-    <hyperlink ref="X12" r:id="rId69" display="mailto:arunsai.sadu@datafactz.com"/>
-    <hyperlink ref="X13" r:id="rId70" display="mailto:santhoshkumar.konduru@datafactz.com"/>
-    <hyperlink ref="X14" r:id="rId71" display="mailto:saivineel.kolla@datafactz.com"/>
-    <hyperlink ref="X15" r:id="rId72"/>
-    <hyperlink ref="X17" r:id="rId73" display="mailto:RajeshKumar.Potharaju@datafactz.com"/>
-    <hyperlink ref="X16" r:id="rId74" display="mailto:SaiKrishna.Arram@datafactz.com"/>
-    <hyperlink ref="X18" r:id="rId75"/>
-    <hyperlink ref="X19" r:id="rId76" display="mailto:Anand.Karnati@datafactz.com"/>
-    <hyperlink ref="X20" r:id="rId77" display="mailto:anantha.chintalapati@datafactz.com"/>
-    <hyperlink ref="X21" r:id="rId78"/>
-    <hyperlink ref="X22" r:id="rId79"/>
-    <hyperlink ref="X23" r:id="rId80"/>
-    <hyperlink ref="X24" r:id="rId81"/>
-    <hyperlink ref="X25" r:id="rId82"/>
-    <hyperlink ref="X26" r:id="rId83" display="mailto:satyasrinivas.matha@datafactz.com"/>
-    <hyperlink ref="X27" r:id="rId84" display="mailto:naveen.tatavarthy@datafactz.com"/>
-    <hyperlink ref="X28" r:id="rId85" display="mailto:praveen.vadde@datafactz.com"/>
-    <hyperlink ref="X30" r:id="rId86"/>
-    <hyperlink ref="X31" r:id="rId87"/>
-    <hyperlink ref="X32" r:id="rId88"/>
-    <hyperlink ref="X33" r:id="rId89"/>
-    <hyperlink ref="X34" r:id="rId90"/>
-    <hyperlink ref="X35" r:id="rId91"/>
-    <hyperlink ref="X36" r:id="rId92"/>
-    <hyperlink ref="X37" r:id="rId93"/>
-    <hyperlink ref="X38" r:id="rId94"/>
-    <hyperlink ref="X39" r:id="rId95"/>
-    <hyperlink ref="X40" r:id="rId96"/>
-    <hyperlink ref="X41" r:id="rId97"/>
-    <hyperlink ref="X42" r:id="rId98"/>
-    <hyperlink ref="X43" r:id="rId99"/>
-    <hyperlink ref="X44" r:id="rId100"/>
-    <hyperlink ref="X45" r:id="rId101"/>
-    <hyperlink ref="X46" r:id="rId102"/>
-    <hyperlink ref="X47" r:id="rId103"/>
-    <hyperlink ref="X48" r:id="rId104"/>
-    <hyperlink ref="X49" r:id="rId105"/>
-    <hyperlink ref="X50" r:id="rId106"/>
-    <hyperlink ref="X51" r:id="rId107"/>
-    <hyperlink ref="X52" r:id="rId108"/>
-    <hyperlink ref="X53" r:id="rId109"/>
-    <hyperlink ref="X54" r:id="rId110"/>
+    <hyperlink ref="S8" r:id="rId50" display="https://micr.bankifsccode.com/520229005"/>
+    <hyperlink ref="S9" r:id="rId51" display="https://micr.bankifsccode.com/560229030"/>
+    <hyperlink ref="S19" r:id="rId52" display="https://micr.bankifsccode.com/411229020"/>
+    <hyperlink ref="S20" r:id="rId53" display="https://micr.bankifsccode.com/500229089"/>
+    <hyperlink ref="S31" r:id="rId54" display="https://micr.bankifsccode.com/600229021"/>
+    <hyperlink ref="S33" r:id="rId55" display="https://micr.bankifsccode.com/504229202"/>
+    <hyperlink ref="S35" r:id="rId56" display="https://micr.bankifsccode.com/500229003"/>
+    <hyperlink ref="S42" r:id="rId57" display="https://micr.bankifsccode.com/523229602"/>
+    <hyperlink ref="P9" r:id="rId58" display="https://bankifsccode.com/ICICI_BANK_LTD/KARNATAKA/BANGALORE_URBAN/BANGALORE_-_SARJAPUR_ROAD"/>
+    <hyperlink ref="W9" r:id="rId59" display="https://bankifsccode.com/ICICI_BANK_LTD/KARNATAKA/BANGALORE_URBAN/BANGALORE_-_SARJAPUR_ROAD"/>
+    <hyperlink ref="X2" r:id="rId60"/>
+    <hyperlink ref="X5" r:id="rId61"/>
+    <hyperlink ref="X6" r:id="rId62"/>
+    <hyperlink ref="X7" r:id="rId63"/>
+    <hyperlink ref="X8" r:id="rId64"/>
+    <hyperlink ref="X9" r:id="rId65"/>
+    <hyperlink ref="X10" r:id="rId66"/>
+    <hyperlink ref="X11" r:id="rId67"/>
+    <hyperlink ref="X12" r:id="rId68" display="mailto:arunsai.sadu@datafactz.com"/>
+    <hyperlink ref="X13" r:id="rId69" display="mailto:santhoshkumar.konduru@datafactz.com"/>
+    <hyperlink ref="X14" r:id="rId70" display="mailto:saivineel.kolla@datafactz.com"/>
+    <hyperlink ref="X15" r:id="rId71"/>
+    <hyperlink ref="X17" r:id="rId72" display="mailto:RajeshKumar.Potharaju@datafactz.com"/>
+    <hyperlink ref="X16" r:id="rId73" display="mailto:SaiKrishna.Arram@datafactz.com"/>
+    <hyperlink ref="X18" r:id="rId74"/>
+    <hyperlink ref="X19" r:id="rId75" display="mailto:Anand.Karnati@datafactz.com"/>
+    <hyperlink ref="X20" r:id="rId76" display="mailto:anantha.chintalapati@datafactz.com"/>
+    <hyperlink ref="X21" r:id="rId77"/>
+    <hyperlink ref="X22" r:id="rId78"/>
+    <hyperlink ref="X23" r:id="rId79"/>
+    <hyperlink ref="X24" r:id="rId80"/>
+    <hyperlink ref="X25" r:id="rId81"/>
+    <hyperlink ref="X26" r:id="rId82" display="mailto:satyasrinivas.matha@datafactz.com"/>
+    <hyperlink ref="X27" r:id="rId83" display="mailto:naveen.tatavarthy@datafactz.com"/>
+    <hyperlink ref="X28" r:id="rId84" display="mailto:praveen.vadde@datafactz.com"/>
+    <hyperlink ref="X30" r:id="rId85"/>
+    <hyperlink ref="X31" r:id="rId86"/>
+    <hyperlink ref="X32" r:id="rId87"/>
+    <hyperlink ref="X33" r:id="rId88"/>
+    <hyperlink ref="X34" r:id="rId89"/>
+    <hyperlink ref="X35" r:id="rId90"/>
+    <hyperlink ref="X36" r:id="rId91"/>
+    <hyperlink ref="X37" r:id="rId92"/>
+    <hyperlink ref="X38" r:id="rId93"/>
+    <hyperlink ref="X39" r:id="rId94"/>
+    <hyperlink ref="X40" r:id="rId95"/>
+    <hyperlink ref="X41" r:id="rId96"/>
+    <hyperlink ref="X42" r:id="rId97"/>
+    <hyperlink ref="X43" r:id="rId98"/>
+    <hyperlink ref="X44" r:id="rId99"/>
+    <hyperlink ref="X45" r:id="rId100"/>
+    <hyperlink ref="X46" r:id="rId101"/>
+    <hyperlink ref="X47" r:id="rId102"/>
+    <hyperlink ref="X48" r:id="rId103"/>
+    <hyperlink ref="X49" r:id="rId104"/>
+    <hyperlink ref="X50" r:id="rId105"/>
+    <hyperlink ref="X51" r:id="rId106"/>
+    <hyperlink ref="X52" r:id="rId107"/>
+    <hyperlink ref="X53" r:id="rId108"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId111"/>
+  <pageSetup orientation="portrait" r:id="rId109"/>
 </worksheet>
 </file>